--- a/docs/CONNECTSPHERE BACKLOGS CAA 091026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 091026.xlsx
@@ -2226,9 +2226,9 @@
 Scenario 6 - Hold expires and frees the venue
 Given my hold's expiry date and time has passed and I have not submitted a booking request for it When the expiry job next runs Then the hold's status becomes Expired, the period returns to Free on the calendar, the venue can be held or requested by any event, and an Expired hold is never counted as a Confirmed or Pending booking anywhere, including the E08-S03 confirmation gate (C-68, T-69)
 Scenario 7 - Coordinator told at expiry
-Given my hold expires When the expiry job runs Then I receive one in-app notice and one email naming the venue, the event and the expiry time, saying the hold has expired and the venue is free; a later run sends nothing more. There is no reminder before expiry (T-78, replacing the O-33 default)
+Given my hold expires When the expiry job runs Then I receive one in-app notice and one email naming the venue, the event and the expiry time, saying the hold has expired and the venue is free; a later run sends nothing more. There is no reminder before expiry (T-79, replacing the O-33 default)
 Scenario 8 - Venue Staff may extend a hold
-Given a hold has not yet expired When Venue Staff set a later expiry date and time Then the new expiry applies, and the extension is recorded in the activity log with who made it; an expired hold cannot be extended and must be placed again (T-78)
+Given a hold has not yet expired When Venue Staff set a later expiry date and time Then the new expiry applies, and the extension is recorded in the activity log with who made it; an expired hold cannot be extended and must be placed again (T-79)
 Scenario 9 - Expiry exactly at the boundary
 Given a hold expires at 10:00:00 When the expiry job runs at 09:59:59 Then the hold is still Tentative, and when it runs at 10:00:00 or later Then the hold is Expired
 Checklist
@@ -2240,7 +2240,7 @@
 - Confirm only one active hold or confirmed booking exists per venue and period
 - See the expiry date and time on every hold, defaulting to 48 hours after creation (assumes O-31)
 - Confirm an expired hold frees the venue and is never treated as a booking
-- Receive one notice, in-app and by email, when a hold expires (T-78)
+- Receive one notice, in-app and by email, when a hold expires (T-79)
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, O-31, O-32, O-33, O-34, T-78</t>
+          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, O-31, O-32, O-33, O-34, T-79</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -5671,9 +5671,9 @@
 Scenario 6 - Hold expires and frees the venue
 Given my hold's expiry date and time has passed and I have not submitted a booking request for it When the expiry job next runs Then the hold's status becomes Expired, the period returns to Free on the calendar, the venue can be held or requested by any event, and an Expired hold is never counted as a Confirmed or Pending booking anywhere, including the E08-S03 confirmation gate (C-68, T-69)
 Scenario 7 - Coordinator told at expiry
-Given my hold expires When the expiry job runs Then I receive one in-app notice and one email naming the venue, the event and the expiry time, saying the hold has expired and the venue is free; a later run sends nothing more. There is no reminder before expiry (T-78, replacing the O-33 default)
+Given my hold expires When the expiry job runs Then I receive one in-app notice and one email naming the venue, the event and the expiry time, saying the hold has expired and the venue is free; a later run sends nothing more. There is no reminder before expiry (T-79, replacing the O-33 default)
 Scenario 8 - Venue Staff may extend a hold
-Given a hold has not yet expired When Venue Staff set a later expiry date and time Then the new expiry applies, and the extension is recorded in the activity log with who made it; an expired hold cannot be extended and must be placed again (T-78)
+Given a hold has not yet expired When Venue Staff set a later expiry date and time Then the new expiry applies, and the extension is recorded in the activity log with who made it; an expired hold cannot be extended and must be placed again (T-79)
 Scenario 9 - Expiry exactly at the boundary
 Given a hold expires at 10:00:00 When the expiry job runs at 09:59:59 Then the hold is still Tentative, and when it runs at 10:00:00 or later Then the hold is Expired
 Checklist
@@ -5685,7 +5685,7 @@
 - Confirm only one active hold or confirmed booking exists per venue and period
 - See the expiry date and time on every hold, defaulting to 48 hours after creation (assumes O-31)
 - Confirm an expired hold frees the venue and is never treated as a booking
-- Receive one notice, in-app and by email, when a hold expires (T-78)
+- Receive one notice, in-app and by email, when a hold expires (T-79)
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, O-31, O-32, O-33, O-34, T-78</t>
+          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, O-31, O-32, O-33, O-34, T-79</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 091026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 091026.xlsx
@@ -3614,7 +3614,7 @@
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
-Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log
+Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log; access-denial entries are not shown in that log
 Scenario 2 - Access denial recorded
 Given a user is denied access to an event or screen When the refusal occurs Then an entry is recorded with the user, the target and the time
 Scenario 3 - Transferred to E06-S04 Scenario 5 (T-76)
@@ -3629,6 +3629,7 @@
 - Record every account deactivation
 - Confirm log entries cannot be edited or deleted by any user
 - Verify that an Event Coordinator can read the event Activity log within existing event access rules
+- Confirm access-denial entries, and the names of the users they refer to, are not shown in the event Activity log
 - Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
@@ -7486,7 +7487,7 @@
       <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
-Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log
+Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log; access-denial entries are not shown in that log
 Scenario 2 - Access denial recorded
 Given a user is denied access to an event or screen When the refusal occurs Then an entry is recorded with the user, the target and the time
 Scenario 3 - Transferred to E06-S04 Scenario 5 (T-76)
@@ -7501,6 +7502,7 @@
 - Record every account deactivation
 - Confirm log entries cannot be edited or deleted by any user
 - Verify that an Event Coordinator can read the event Activity log within existing event access rules
+- Confirm access-denial entries, and the names of the users they refer to, are not shown in the event Activity log
 - Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 091026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 091026.xlsx
@@ -2227,10 +2227,10 @@
 Given a venue has a setup time of 30 minutes and a turnaround time of 45 minutes When I hold it tentatively for 10:00 to 12:00 Then the hold occupies 09:30 to 12:45, the calendar shows that window as Tentative, and another hold or booking request overlapping any part of it is refused (C-65, T-66)
 Scenario 6 - Hold expires and frees the venue
 Given my hold's expiry date and time has passed and I have not submitted a booking request for it When the expiry job next runs Then the hold's status becomes Expired, the period returns to Free on the calendar, the venue can be held or requested by any event, and an Expired hold is never counted as a Confirmed or Pending booking anywhere, including the E08-S03 confirmation gate (C-68, T-69)
-Scenario 7 - Coordinator told before and at expiry
-Given my hold will expire in 24 hours When that moment passes Then I receive an in-app and email reminder naming the venue, the event and the expiry time; and Given the hold expires When the expiry job runs Then I receive an in-app and email notice that it has expired and the venue is free (assumes O-33)
+Scenario 7 - Coordinator told at expiry
+Given my hold expires When the expiry job runs Then I receive one in-app notice and one email naming the venue, the event and the expiry time, saying the hold has expired and the venue is free; a later run sends nothing more. There is no reminder before expiry (T-79, replacing the O-33 default)
 Scenario 8 - Venue Staff may extend a hold
-Given a hold has not yet expired When Venue Staff set a later expiry date and time Then the new expiry applies, the extension is recorded in the activity log with who made it, and the reminder is rescheduled; an expired hold cannot be extended and must be placed again (assumes O-34)
+Given a hold has not yet expired When Venue Staff set a later expiry date and time Then the new expiry applies, and the extension is recorded in the activity log with who made it; an expired hold cannot be extended and must be placed again (T-79)
 Scenario 9 - Expiry exactly at the boundary
 Given a hold expires at 10:00:00 When the expiry job runs at 09:59:59 Then the hold is still Tentative, and when it runs at 10:00:00 or later Then the hold is Expired
 Checklist
@@ -2242,7 +2242,7 @@
 - Confirm only one active hold or confirmed booking exists per venue and period
 - See the expiry date and time on every hold, defaulting to 48 hours after creation (assumes O-31)
 - Confirm an expired hold frees the venue and is never treated as a booking
-- Receive a reminder before and a notice at expiry (assumes O-33)
+- Receive one notice, in-app and by email, when a hold expires (T-79)
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, O-31, O-32, O-33, O-34</t>
+          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, T-79, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
 Given a venue has a setup time of 30 minutes and a turnaround time of 45 minutes When I hold it tentatively for 10:00 to 12:00 Then the hold occupies 09:30 to 12:45, the calendar shows that window as Tentative, and another hold or booking request overlapping any part of it is refused (C-65, T-66)
 Scenario 6 - Hold expires and frees the venue
 Given my hold's expiry date and time has passed and I have not submitted a booking request for it When the expiry job next runs Then the hold's status becomes Expired, the period returns to Free on the calendar, the venue can be held or requested by any event, and an Expired hold is never counted as a Confirmed or Pending booking anywhere, including the E08-S03 confirmation gate (C-68, T-69)
-Scenario 7 - Coordinator told before and at expiry
-Given my hold will expire in 24 hours When that moment passes Then I receive an in-app and email reminder naming the venue, the event and the expiry time; and Given the hold expires When the expiry job runs Then I receive an in-app and email notice that it has expired and the venue is free (assumes O-33)
+Scenario 7 - Coordinator told at expiry
+Given my hold expires When the expiry job runs Then I receive one in-app notice and one email naming the venue, the event and the expiry time, saying the hold has expired and the venue is free; a later run sends nothing more. There is no reminder before expiry (T-79, replacing the O-33 default)
 Scenario 8 - Venue Staff may extend a hold
-Given a hold has not yet expired When Venue Staff set a later expiry date and time Then the new expiry applies, the extension is recorded in the activity log with who made it, and the reminder is rescheduled; an expired hold cannot be extended and must be placed again (assumes O-34)
+Given a hold has not yet expired When Venue Staff set a later expiry date and time Then the new expiry applies, and the extension is recorded in the activity log with who made it; an expired hold cannot be extended and must be placed again (T-79)
 Scenario 9 - Expiry exactly at the boundary
 Given a hold expires at 10:00:00 When the expiry job runs at 09:59:59 Then the hold is still Tentative, and when it runs at 10:00:00 or later Then the hold is Expired
 Checklist
@@ -5690,7 +5690,7 @@
 - Confirm only one active hold or confirmed booking exists per venue and period
 - See the expiry date and time on every hold, defaulting to 48 hours after creation (assumes O-31)
 - Confirm an expired hold frees the venue and is never treated as a booking
-- Receive a reminder before and a notice at expiry (assumes O-33)
+- Receive one notice, in-app and by email, when a hold expires (T-79)
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, O-31, O-32, O-33, O-34</t>
+          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, T-79, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
